--- a/artfynd/A 51019-2024 artfynd.xlsx
+++ b/artfynd/A 51019-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122545861</v>
       </c>
       <c r="B2" t="n">
-        <v>105317</v>
+        <v>105330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -692,6 +692,11 @@
       </c>
       <c r="E2" t="n">
         <v>221144</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>

--- a/artfynd/A 51019-2024 artfynd.xlsx
+++ b/artfynd/A 51019-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122545861</v>
       </c>
       <c r="B2" t="n">
-        <v>105330</v>
+        <v>105343</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 51019-2024 artfynd.xlsx
+++ b/artfynd/A 51019-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122545861</v>
       </c>
       <c r="B2" t="n">
-        <v>105343</v>
+        <v>105346</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 51019-2024 artfynd.xlsx
+++ b/artfynd/A 51019-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122545861</v>
       </c>
       <c r="B2" t="n">
-        <v>105346</v>
+        <v>105347</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 51019-2024 artfynd.xlsx
+++ b/artfynd/A 51019-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122545861</v>
       </c>
       <c r="B2" t="n">
-        <v>105347</v>
+        <v>105350</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 51019-2024 artfynd.xlsx
+++ b/artfynd/A 51019-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122545861</v>
       </c>
       <c r="B2" t="n">
-        <v>105453</v>
+        <v>105461</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 51019-2024 artfynd.xlsx
+++ b/artfynd/A 51019-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122545861</v>
       </c>
       <c r="B2" t="n">
-        <v>105461</v>
+        <v>105463</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 51019-2024 artfynd.xlsx
+++ b/artfynd/A 51019-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -783,6 +783,108 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124811073</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91032</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Vibrostugan, Vibrostugan, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>646902</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6546039</v>
+      </c>
+      <c r="S3" t="n">
+        <v>4</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hölö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Eva Siljeholm</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51019-2024 artfynd.xlsx
+++ b/artfynd/A 51019-2024 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>124811073</v>
       </c>
       <c r="B3" t="n">
-        <v>91032</v>
+        <v>91186</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
